--- a/data/combat_styles.xlsx
+++ b/data/combat_styles.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Archery" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Armored Fighting" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Brawling" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Crossbow Fighting" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dueling" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Great Weapon Fighting" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Missile Skirmishing" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Shield Fighting" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Spear &amp; Polearm Fighting" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Two-Weapon Fighting" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archery" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armored Fighting" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brawling" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crossbow Fighting" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dueling" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Great Weapon Fighting" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile Skirmishing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shield Fighting" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spear &amp; Polearm Fighting" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Two-Weapon Fighting" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -447,6 +447,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -475,6 +476,11 @@
           <t>Meta note</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -502,6 +508,11 @@
           <t>bows and careful ranged attacks</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -529,6 +540,11 @@
           <t>the harness as a weapon</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -556,6 +572,11 @@
           <t>fists, feet, tusks, headbutts</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -583,6 +604,11 @@
           <t>prepared mechanical ranged weapons</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -610,6 +636,11 @@
           <t>one one-handed weapon, other hand free</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -637,6 +668,11 @@
           <t>two hands, full commitment</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -664,6 +700,11 @@
           <t>slings, thrown weapons, bolas</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -691,6 +732,11 @@
           <t>weapon and shield as one machine</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -718,6 +764,11 @@
           <t>polearms and spears</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -743,6 +794,11 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>a weapon in each hand</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Melee</t>
         </is>
       </c>
     </row>
@@ -839,11 +895,32 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency.
-You gain the Keep Measure ◆ action.
-Keep Measure ◆ (stance)
-Requirements You are wielding a hafted weapon.
-While in this stance: the first time each round an enemy moves from outside your Reach into it, you may Step 3 feet directly away as a free action after that movement finishes; if that movement keeps the enemy within your Reach, it does not trigger reactions from that enemy. Every talent here requires this.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank. You gain the Keep Measure ❶ action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Keep Measure ❶ Stance</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wielding a Hafted weapon.
+While in this stance:
+The first time each round an enemy moves from outside your Reach into it, you may Step ⓿ directly away after that movement finishes.
+If that movement keeps the enemy within your Reach, it does not trigger Reactions from that enemy.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -852,7 +929,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Set Against the Charge ↺</t>
+          <t>Set Against the Charge</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -870,8 +947,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Trigger A creature moves into your reach.
-Effect Strike it. If it entered from outside your reach, your weapon deals +2 damage per weapon die.</t>
+          <t>When you Intercept with a Spear &amp; Polearm weapon, it deals +2 damage per weapon die. Set, the spear is at its most dangerous the moment the enemy arrives.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -880,7 +956,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Short Grip Strike ◆</t>
+          <t>Short Grip Strike ❶</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -898,9 +974,26 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Flourish
-Requirements You are wielding a hafted weapon.
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Flourish</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wielding a Hafted weapon.
 Reduce your weapon's Unwieldy value by 2 ft.</t>
+          </r>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -931,7 +1024,7 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Increase hafted weapon Reach by 2 ft while using two hands.</t>
+          <t>Increase Hafted Weapon Reach by 2 ft while using two hands.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -958,7 +1051,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>If you Attack a foe and it results in a Graze, you may Step instead of Exposing a Zone.</t>
+          <t>When one of your Strikes is Stopped and would Expose you, you may Step directly away from the target instead.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -967,7 +1060,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sleek Reposition ◆</t>
+          <t>Sleek Reposition ❶</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -985,9 +1078,27 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Press
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Press</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
 While your opponent is still recovering from your prior attack, you snag its armor, clothing, or flesh to move it as you please. Make a melee Strike with a spear or polearm. If you hit a target that is your size or smaller, you can automatically Reposition it, with the same benefits as the Reposition action (including the Critical Success effect, if your Strike was a Critical Hit). Use your Total Reach for this Reposition.
-Failure The target becomes Off-Guard until the end of your current turn.</t>
+This Strike has the following failure effect:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Failure</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The target becomes Off-Guard until your next Opportunity.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -1086,9 +1197,37 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency. Every talent here requires this.
-You gain the Twin Openings action.
-Twin Openings ◆ (stance) You must have a weapon in each hand. While you are in this stance, the first time each turn that you hit the same creature with both of your weapons, you may make one of its zones Exposed after resolving the attack and damage.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank. Every talent here requires this. You gain the Twin Openings action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Twin Openings ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You must have a weapon in each hand. While you are in this stance, the first time each round that you hit the same creature with </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>both</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> of your weapons, you may make one of its zones </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Exposed</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> after resolving the attack and damage.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1097,7 +1236,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Double Slice ◆◆</t>
+          <t>Double Slice ❷</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1115,7 +1254,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Strike with each weapon at your current multiple attack penalty; combine the damage for purposes of bypassing Protection.</t>
+          <t>Quick Strike with each weapon against the same target, one roll for each. Combine the damage of both blows before subtracting Protection.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -1142,7 +1281,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+1 circumstance to Guard while wielding two weapons and not raising a shield.</t>
+          <t>+1 Situation to Guard while wielding two weapons and not raising a shield.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1163,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1245,11 +1384,24 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency.
-You gain the Draw a Bead ◆ action.
-Draw a Bead ◆ (concentrate)
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its Talents call for use this Constellation's Proficiency. Attack rolls use your Ranged Proficiency, and every Talent here counts toward your Ranged rank. You gain the Draw a Bead ❶ action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Draw a Bead ❶ Concentrate</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
 Choose one creature you can Observe and can reach with your bow.
-Until the end of your turn: your next bow Strike against that creature gains a +1 circumstance bonus to the attack; ignore the weapon's Unwieldy penalty for that Strike; if that Strike Grazes, you choose the Zone that becomes Exposed instead of the defender. Every talent here requires this.</t>
+Until the end of your next Opportunity:
+your next bow Strike against that creature gains a +1 Situation bonus to the attack;
+ignore the weapon's Unwieldy penalty for that Strike;
+if that Strike Grazes, you choose the Zone it lands on instead of the defender.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1289,7 +1441,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Loose and Move</t>
+          <t>Close Shot</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1307,38 +1459,11 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>After making a Strike with a bow, you may Step 3 feet as a free action once per turn.</t>
+          <t>Reduce the minimum distance of Unwieldy by 5 feet. If that would reduce it to 0, the weapon no longer has Unwieldy for you.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Close Shot</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Archery Training</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Reduce the Unwieldy distance of your bow by 5 feet. If that would reduce it to 0, the weapon no longer has Unwieldy for you.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1437,8 +1562,8 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency.
-When determining whether your armor forms a complete harness for an Armored Fighting Talent, all four Zones must be armored in the required material. If you are Master, only three Zones must be armored in the required material. Every talent here requires this.</t>
+          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank.
+When determining whether your armor forms a complete harness for an Armored Fighting Talent, all four Zones must be armored in the required material. If you are Master, only three Zones must be armored in the required material.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1473,7 +1598,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>While wearing Full Plate, gain a +1 status bonus to Guard for physical Attacks against Shove, Trip, and Reposition.</t>
+          <t>While wearing Full Plate, gain +1 Condition bonus Physical Guard against Shove, Trip, and Reposition.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1517,7 +1642,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Lock Down ◆</t>
+          <t>Lock Down ❶</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1535,8 +1660,22 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>You settle your weight into your Full Plate harness.
-While in this Stance: +1 status bonus to Guard for physical Attacks; you cannot be forcibly moved more than 3 feet by a single effect unless it critically succeeds; your Speed is reduced by 5 feet.</t>
+          <r>
+            <t xml:space="preserve">You settle your weight into your Full Plate harness.
+While in this </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Stance</t>
+          </r>
+          <r>
+            <t>:
++1 Condition bonus to Physical Guard.
+You cannot be forcibly moved more than 3 feet by a single effect unless it critically succeeds.
+Your Speed is reduced by 1 foot.</t>
+          </r>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1571,7 +1710,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>When you successfully Shove a creature, that creature takes an amount of bludgeoning damage equal to your Might modifier (or double that amount on a Critical Success). This damage increases by 2 when you become Expert in Armored Fighting, 6 when you become Master, and 12 when you become Legendary.</t>
+          <t>When you successfully Shove a creature, that creature takes an amount of bludgeoning damage equal to your Might modifier (or double that amount on a Critical Success). This damage increases by 2 when you become an expert in Armored Fighting, 6 when you become a master, and 12 when you become legendary.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1584,7 +1723,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Shoulder Check ◆</t>
+          <t>Shoulder Check ❶</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1602,10 +1741,39 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>You hit a foe with your armor to throw them off balance. Make a fist Strike even if you don't have a hand free; if you're wielding a gauntlet or spiked gauntlet, you can make a Strike with one of those weapons instead. The Strike gains the following additional results:
-Critical Success The target is Wrong-Footed for you until the end of your next turn.
-Success The target is Wrong-Footed for you against the next Attack you attempt against it before the end of your current turn.
-Critical Failure You are Wrong-Footed against melee attacks the target attempts against you until the end of your next turn.</t>
+          <r>
+            <t xml:space="preserve">You hit a foe with your armor to throw them off balance. Make a fist Strike even if you don't have a hand free; if you're wielding a gauntlet or spiked gauntlet, you can make a Strike with one of those weapons instead. The Strike gains the following additional results:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Critical Success</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The target is Wrong-Footed for you until the end of the next round.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Success</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The target is Wrong-Footed for you against the next Attack you attempt against it before the end of your next Opportunity.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Critical Failure</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are Wrong-Footed against melee attacks the target attempts against you until the end of the next round.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1618,7 +1786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Flowing Defense ◆</t>
+          <t>Flowing Defense ❶</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1636,8 +1804,19 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Flowing Defense ◆ (stance)
-While wearing Full Mail: when you Recenter, you may also Step 3 feet; −1 status penalty to Guard for physical Attacks versus Shove; retains mail's normal vulnerability to piercing.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Flowing Defense ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+While wearing Full Mail:
+when you Recenter, you may also Step;
+-1 Condition Physical Guard versus Shove
+retains mail's normal vulnerability to piercing</t>
+          </r>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -1664,7 +1843,7 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Your first Step each turn ignores 1 point of Load Strain's effect on movement-related checks.</t>
+          <t>Your first Step each round ignores 1 point of Load Strain's effect on movement-related checks.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -1673,7 +1852,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Roll With It ↺</t>
+          <t>Roll With It ❶↺</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1691,7 +1870,7 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>When you are Grazed while wearing Full Mail, you may Step 3 feet after resolving the attack and damage.</t>
+          <t>When you are Grazed while wearing Full Mail, you may Step after resolving the attack and damage.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -1700,7 +1879,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Turn the Scales ↺</t>
+          <t>Turn the Scales ❶↺</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1718,7 +1897,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Once per round when you would be Hit, shift the blow to another armored, non-Exposed Zone.</t>
+          <t>When you would be Hit, shift the blow to another armored, non-Exposed Zone.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1731,7 +1910,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Layered Guard ◆</t>
+          <t>Layered Guard ❶</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1749,8 +1928,17 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Layered Guard ◆ (stance)
-While wearing Full Scale: the first time each round a Zone becomes Exposed, another Zone of your choice gains +1 Protection until the start of your next turn.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Layered Guard ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+While wearing Full Scale:
+the first time each round a Zone becomes Exposed, another Zone of your choice gains +1 Protection until your next Opportunity.</t>
+          </r>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1781,7 +1969,7 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>While all four Zones are Padded or Leather and your Load Strain is 0, Recenter lets you Step 3 feet as part of the action.</t>
+          <t>While all four Zones are Padded or Leather and your Load Strain is 0, Recenter lets you Step as part of the action.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1794,7 +1982,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Light on Your Feet ◆</t>
+          <t>Light on Your Feet ❶</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1812,8 +2000,19 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Light on Your Feet ◆ (stance)
-While in light armor: +1 status bonus to Evade for physical Attacks; after a creature Misses you, Step 3 feet once per round. Cannot be used if your Load Strain exceeds 0.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Light on Your Feet ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+While in light armor:
++1 Condition Physical Evade;
+After a creature Misses you, Step once per round;
+Cannot be used if Load Strain exceeds 0.</t>
+          </r>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1916,9 +2115,19 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency. Every talent here requires this.
-You gain the Clinch action.
-Clinch ◆ (stance) While you are in this stance, when you Graze an enemy with a Strike, you choose which of its Zones is Exposed, rather than the enemy. At Master rank, a creature you have Grabbed cannot Recenter.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank. Every talent here requires this. You gain the Clinch action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Clinch ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> While you are in this stance, a bare hand counts as a rigid implement: you may Parry, Bind, and Gain Control with it, and a creature whose weapon or limb you Control with a bare hand is also Grabbed. At Master rank, a creature you have Grabbed cannot Recenter.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1954,7 +2163,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Snagging Grip ◆</t>
+          <t>Snagging Grip ❶</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1972,7 +2181,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Strike with a free hand; on a hit, the target is Off-Guard until your next turn.</t>
+          <t>Strike with a free hand; on a hit, the target is Off-Guard until your next Opportunity.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -2098,10 +2307,34 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency.
-You gain the Brace the Stock ◆ action.
-Brace the Stock ◆ (stance)
-You settle into a firing position. Until you Move: gain a +1 circumstance bonus to all crossbow Strikes; increase any Armor-Piercing [N] value of those attacks by 1; if the attack Grazes, you choose the Zone that becomes Exposed. The effect ends after you make a Move. Every talent here requires this.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Ranged Proficiency, and every Talent here counts toward your Ranged rank. You gain the Brace the Stock ❶ action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Brace the Stock ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+You settle into a firing position.
+Until you Move:
+gain a +1 Situation bonus to all crossbow Strikes;
+increase any Armor-Piercing [N] value of those attacks by 1;
+if the attack Grazes, you choose the Zone it lands on.
+The effect ends after you make a </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Move</t>
+          </r>
+          <r>
+            <t>.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -2128,7 +2361,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Once per turn, reduce the Reload value of a crossbow by 1, to a minimum of 1.</t>
+          <t>Once per round, reduce the Reload value of a crossbow by 1, to a minimum of 1.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2159,7 +2392,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>When you spend an action Reloading, you may Step 3 feet as part of that action.</t>
+          <t>When you spend an action Reloading, you may Step as part of that action.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -2213,7 +2446,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>You may use a loaded crossbow with the Close trait to make Reactive Strikes if you have an ability that grants them.</t>
+          <t>You may Intercept ❶↺ with a loaded crossbow that has the Close trait, if you have the Intercept Reaction.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2222,7 +2455,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Covered Reload ◆</t>
+          <t>Covered Reload ❶</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2339,9 +2572,28 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency. Every talent here requires this.
-You gain the Measure action.
-The Measure ◆ (stance) You must wield a single one-handed weapon with your other hand free. Name one creature as you enter the stance. That creature must answer your Strikes with the same Defense it used against your previous Strike, until you leave the stance or name another. At Master rank you may name a new creature as a free action.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank. Every talent here requires this. You gain the Hold the Cadence action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Hold the Cadence ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You must wield a single one-handed weapon with your other hand free. Name one creature as you enter the stance. That creature must answer your Strikes with the </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>same Defense it used against your previous Strike</t>
+          </r>
+          <r>
+            <t>, until you leave the stance or name another. At Master rank you may name a new creature ⓿.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -2368,7 +2620,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+1 circumstance Guard vs. melee while wielding a one-handed weapon with your other hand free.</t>
+          <t>+1 Situation Guard vs. melee while wielding a one-handed weapon with your other hand free.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2381,7 +2633,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Feinting Lunge ◆◆</t>
+          <t>Feinting Lunge ❷</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2408,7 +2660,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Snagging Strike ◆</t>
+          <t>Snagging Strike ❶</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2426,7 +2678,7 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>You combine an attack with quick grappling moves to throw an enemy off balance as long as it stays in your reach. Make a Strike while keeping one hand free. If this Strike hits, the target is Off-Guard until the start of your next turn or until it's no longer within the reach of your hand, whichever comes first.</t>
+          <t>You combine an attack with quick grappling moves to throw an enemy off balance as long as it stays in your reach. Make a Strike while keeping one hand free. If this Strike hits, the target is Off-Guard until your next Opportunity or until it's no longer within the reach of your hand, whichever comes first.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -2435,7 +2687,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Combat Grab ◆</t>
+          <t>Combat Grab ❶</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2453,9 +2705,26 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Press
-Requirements You have one hand free, and your target is within reach of that hand.
-Using your prior attack to shift your opponent's guard, you take another swing and grab them. Make a melee Strike while keeping one hand free. If the Strike hits, you grab the target using your free hand. The creature remains grabbed until the end of your next turn or until it Escapes, whichever comes first.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Press</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You have one hand free, and your target is within reach of that hand
+Using your prior attack to shift your opponent's guard, you take another swing and grab them. Make a melee Strike while keeping one hand free. If the Strike hits, you grab the target using your free hand. The creature remains grabbed until the end of the next round or until it Escapes, whichever comes first.</t>
+          </r>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2468,7 +2737,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Dueling Parry ◆</t>
+          <t>Dueling Parry ❶</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2486,8 +2755,25 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Requirements You are wielding a single one-handed melee weapon and hold nothing else in your hands.
-You can parry attacks against you with your one-handed weapon. You gain a +2 circumstance bonus to Guard until the start of your next turn as long as you continue to meet the requirements.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wielding a single one-handed melee weapon and hold nothing else in your hands
+You can parry attacks against you with your one-handed weapon. You gain a +2 Situation bonus to </t>
+          </r>
+          <r>
+            <rPr>
+              <i val="1"/>
+            </rPr>
+            <t>Guard</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> until your next Opportunity as long as you continue to meet the requirements.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2590,11 +2876,21 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency.
-You gain the Overreach action.
-Overreach ◆ (stance)
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank. You gain the Overreach action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Overreach ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
 You must be wielding a two-handed melee weapon.
 While you are in this stance your Hits and Critical Hits deal +2 damage and your Evade drops by 2, rising to +3 damage at Expert rank, +4 at Master, and +5 at Legendary. Every talent here requires this.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -2603,7 +2899,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sweeping Blow ◆◆</t>
+          <t>Sweeping Blow ❷</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2621,7 +2917,18 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>One attack roll against two creatures within your reach, resolved separately against each one's chosen Defense. Both count as a single attack for your multiple attack penalty.</t>
+          <r>
+            <t xml:space="preserve">One attack roll against two creatures within your reach, resolved separately against each one's chosen Defense. This Strike is </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Weighted</t>
+          </r>
+          <r>
+            <t>.</t>
+          </r>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -2648,7 +2955,18 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>When your Strike drops a creature, your next Strike this turn ignores your multiple attack penalty.</t>
+          <r>
+            <t xml:space="preserve">When your Strike drops a creature, your next Strike this round against another creature is not </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Weighted</t>
+          </r>
+          <r>
+            <t>.</t>
+          </r>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -2657,7 +2975,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Brutish Shove ◆</t>
+          <t>Brutish Shove ❶</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2675,9 +2993,26 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Requirements You are wielding a two-handed melee weapon.
-Using the momentum of your last attack to throw your weight into another, you make your opponent stumble back. Make a Strike with a two-handed melee weapon. If you hit a target that is your size or smaller, that creature is Off-Guard until the end of your current turn, and you can automatically Shove it, with the same benefits as the Shove action (including the Critical Success effect, if your Strike was a Critical Hit). If you move to follow the target, your movement doesn't trigger reactions.
-Failure The target becomes Off-Guard until the end of your current turn.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wielding a two-handed melee weapon
+Using the momentum of your last attack to throw your weight into another, you make your opponent stumble back. Make a Strike with a two-handed melee weapon. If you hit a target that is your size or smaller, that creature is Off-Guard until your next Opportunity, and you can automatically Shove it, with the same benefits as the Shove action (including the Critical Success effect, if your Strike was a Critical Hit). If you move to follow the target, your movement doesn't trigger Reactions. This Strike has the following failure effect:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Failure</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The target becomes Off-Guard until your next Opportunity.</t>
+          </r>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -2704,7 +3039,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>When you make a Strike ◆◆◆ with a two-handed weapon, deal one extra weapon die of damage.</t>
+          <t>When you make a Strike ❸ with a two-handed weapon, deal one extra weapon die of damage.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2830,11 +3165,32 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency.
-You gain the Keep Moving ◆ action.
-Keep Moving ◆ (stance)
-Requirements You wield a sling or a weapon with the Thrown trait.
-While in this stance: if you make a ranged Strike, you may Step 3 feet immediately before or after it; you may use this benefit only once per turn. Every talent here requires this.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Ranged Proficiency, and every Talent here counts toward your Ranged rank. You gain the Keep Moving ❶ action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Keep Moving ❶ Stance</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You wield a sling or a weapon with the Thrown trait.
+While in this stance:
+if you make a ranged Strike, you may Step immediately before or after it;
+you may use this benefit only once per round.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -2888,7 +3244,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>If you Strided at least 5 feet immediately before making a ranged Strike with a sling or thrown weapon, increase its Range by 10 feet for that Strike.</t>
+          <t>If you Moved at least 3 feet immediately before making a ranged Strike with a sling or thrown weapon, increase its Range by 10 feet for that Strike.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -2915,7 +3271,7 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>When you Graze with a sling or thrown weapon, the target takes a −1 circumstance penalty to its next Attack before the end of its next turn.</t>
+          <t>When you Graze with a sling or thrown weapon, the target takes a −1 Situation penalty to its next Attack before the end of the next round.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -2942,7 +3298,18 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>You get a +2 status bonus to your Trip checks when using a Ranged weapon with the Trip trait.</t>
+          <r>
+            <t xml:space="preserve">You get a +2 Condition bonus to your Trip checks when using a Ranged weapon with the </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Trip</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Trait.</t>
+          </r>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2951,7 +3318,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Rebounding Toss ◆◆</t>
+          <t>Rebounding Toss ❷</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2969,8 +3336,16 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Requirements You are wielding a thrown weapon.
-You bounce your weapon off one foe to strike another. Make a ranged Strike with a thrown weapon. If this Strike hits, the weapon rebounds toward an enemy within 10 feet of the original target. Make an additional Strike against this second target. Both attacks count toward your multiple attack penalty, but the penalty doesn't increase until after you've made both attacks.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wielding a thrown weapon
+You bounce your weapon off one foe to strike another. Make a ranged Strike with a thrown weapon. If this Strike hits, the weapon rebounds toward an enemy within 10 feet of the original target. Make an additional Strike against this second target. Both are Quick Strikes.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -3073,9 +3448,28 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls themselves use your Weapons Proficiency. Every talent here requires this.
-You gain the Shield Wall action.
-Shield Wall ◆ (stance) You must be wielding a shield. While you are in this stance your shield counts as Raised at all times, without spending an action for it, but you cannot Stride; you may only Step. At Master rank you may Stride up to half your Speed while the stance holds.</t>
+          <r>
+            <t xml:space="preserve">You are Trained in this fighting style: its exploits are open to you, and checks its talents call for use this Constellation's Proficiency. Attack rolls use your Melee Proficiency, and every Talent here counts toward your Melee rank. Every talent here requires this. You gain the Shield Wall action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Shield Wall ❶ Stance</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You must be wielding a shield. While you are in this stance your shield counts as </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Raised at all times</t>
+          </r>
+          <r>
+            <t>, without spending an action for it, but you cannot Move; you may only Step. At Master rank you may Move up to half your Speed while the stance holds.</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -3084,7 +3478,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Reactive Shield ↺</t>
+          <t>Reactive Shield ❶↺</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -3115,7 +3509,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Shield Block ↺</t>
+          <t>Shield Block ❶↺</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3142,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Aggressive Block ◇</t>
+          <t>Aggressive Block ⓿</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3160,8 +3554,16 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Trigger You use Shield Block ↺, and the opponent that triggered Shield Block is adjacent to you and is your size or smaller.
-You push back as you block, knocking your foe away or off balance. You use your shield to push the triggering creature, either automatically Shoving it 5 feet or causing it to become Off-Guard until the start of your next turn. The triggering creature chooses whether to be moved or become Off-Guard. If it chooses to be moved, you choose the direction. If the Shove would cause it to hit a solid object or enter another creature's space, it must become Off-Guard instead of being moved.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You use Shield Block, and the opponent that triggered Shield Block is adjacent to you and is your Size or smaller
+You push back as you block, knocking your foe away or off balance. You use your shield to push the triggering creature, either automatically Shoving it 3 feet or causing it to become Off-Guard until your next Opportunity. The triggering creature chooses whether to be moved or become Off-Guard. If it chooses to be moved, you choose the direction. If the Shove would cause it to hit a solid object or enter another creature's space, it must become Off-Guard instead of being moved.</t>
+          </r>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -3174,7 +3576,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Devoted Guardian ◆</t>
+          <t>Devoted Guardian ❶</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3192,8 +3594,25 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Requirements Your last action was to Raise a Shield.
-You adopt a wide stance, ready to defend both yourself and your chosen ward. Select one adjacent creature. As long as your shield is raised and the creature remains adjacent to you, the creature gains a +1 circumstance bonus to their Guard, or a +2 circumstance bonus if the shield you raised was a tower shield.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Your last action was to Raise a Shield.
+You adopt a wide stance, ready to defend both yourself and your chosen ward. Select one adjacent creature. As long as your shield is raised and the creature remains adjacent to you, the creature gains a +1 Situation bonus to their </t>
+          </r>
+          <r>
+            <rPr>
+              <i val="1"/>
+            </rPr>
+            <t>Guard</t>
+          </r>
+          <r>
+            <t>, or a +2 Situation bonus if the shield you raised was a tower shield.</t>
+          </r>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -3202,7 +3621,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Defensive Advance ◆◆</t>
+          <t>Defensive Advance ❷</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3220,8 +3639,16 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Flourish
-With the protection of your shield, you dive into battle. You Raise your Shield and Stride. If you end your movement within melee reach of at least one enemy, you can make a melee Strike against that enemy. You can use Defensive Advance while Burrowing, Climbing, Flying, or Swimming instead of Striding if you have the corresponding movement type.</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Flourish</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+With the protection of your shield, you dive into battle! You Raise your Shield and Move. If you end your movement within melee reach of at least one enemy, you can make a melee Strike against that enemy. You can use Defensive Advance while Burrowing, Climbing, Flying, or Swimming instead of Moving if you have the corresponding movement type.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>

--- a/data/combat_styles.xlsx
+++ b/data/combat_styles.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5625" yWindow="5625" windowWidth="36450" windowHeight="13980" tabRatio="600" firstSheet="2" activeTab="10" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,14 +19,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Two-Weapon Fighting" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,9 +35,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,7 +60,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E5F6B"/>
+        <fgColor rgb="FF0E5F6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +86,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -482,7 +492,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Archery</t>
@@ -514,7 +524,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting</t>
@@ -546,7 +556,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Brawling</t>
@@ -578,7 +588,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting</t>
@@ -610,7 +620,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Dueling</t>
@@ -642,7 +652,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Fighting</t>
@@ -674,7 +684,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing</t>
@@ -706,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting</t>
@@ -738,7 +748,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Fighting</t>
@@ -770,7 +780,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Two-Weapon Fighting</t>
@@ -813,14 +823,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -873,8 +881,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Training</t>
@@ -890,9 +903,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -903,17 +916,8 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>Keep Measure ❶ Stance</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>Requirements</t>
+            <t>Keep Measure ❶ Stance
+Requirements</t>
           </r>
           <r>
             <t xml:space="preserve"> You are wielding a Hafted weapon.
@@ -923,10 +927,10 @@
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Set Against the Charge</t>
@@ -937,23 +941,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>When you Intercept with a Spear &amp; Polearm weapon, it deals +2 damage per weapon die. Set, the spear is at its most dangerous the moment the enemy arrives.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Short Grip Strike ❶</t>
@@ -964,31 +968,22 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>Flourish</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>Requirements</t>
+            <t>Flourish
+Requirements</t>
           </r>
           <r>
             <t xml:space="preserve"> You are wielding a Hafted weapon.
@@ -1001,7 +996,7 @@
           <t>Agility</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1014,23 +1009,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Increase Hafted Weapon Reach by 2 ft while using two hands.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Keep Away</t>
@@ -1041,23 +1036,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>When one of your Strikes is Stopped and would Expose you, you may Step directly away from the target instead.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="105" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Sleek Reposition ❶</t>
@@ -1068,23 +1063,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Spear &amp; Polearm Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Press</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 While your opponent is still recovering from your prior attack, you snag its armor, clothing, or flesh to move it as you please. Make a melee Strike with a spear or polearm. If you hit a target that is your size or smaller, you can automatically Reposition it, with the same benefits as the Reposition action (including the Critical Success effect, if your Strike was a Critical Hit). Use your Total Reach for this Reposition.
 This Strike has the following failure effect:
@@ -1092,17 +1096,26 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Failure</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> The target becomes Off-Guard until your next Opportunity.</t>
           </r>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1115,14 +1128,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1175,8 +1186,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Two-Weapon Fighting Training</t>
@@ -1192,9 +1208,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -1203,37 +1219,64 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Twin Openings ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You must have a weapon in each hand. While you are in this stance, the first time each round that you hit the same creature with </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>both</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> of your weapons, you may make one of its zones </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Exposed</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> after resolving the attack and damage.</t>
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Double Slice ❷</t>
@@ -1244,23 +1287,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Two-Weapon Fighting Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Quick Strike with each weapon against the same target, one roll for each. Combine the damage of both blows before subtracting Protection.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Off-Hand Guard</t>
@@ -1271,14 +1314,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Two-Weapon Fighting Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>+1 Situation to Guard while wielding two weapons and not raising a shield.</t>
@@ -1289,7 +1332,7 @@
           <t>Presence</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1302,14 +1345,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1362,8 +1403,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="135" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Archery Training</t>
@@ -1379,9 +1425,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -1390,11 +1436,20 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Draw a Bead ❶ Concentrate</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 Choose one creature you can Observe and can reach with your bow.
 Until the end of your next Opportunity:
@@ -1404,8 +1459,8 @@
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1418,14 +1473,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Archery Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Your ranged attacks treat Lesser Cover as no Cover.</t>
@@ -1436,9 +1491,9 @@
           <t>Wits</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Close Shot</t>
@@ -1449,21 +1504,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Archery Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Reduce the minimum distance of Unwieldy by 5 feet. If that would reduce it to 0, the weapon no longer has Unwieldy for you.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1476,14 +1531,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1536,8 +1589,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
@@ -1553,8 +1611,8 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Knowing how to exploit armor as part of your fighting method.</t>
@@ -1571,9 +1629,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Ironclad</t>
@@ -1584,13 +1642,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>You're not harder to hit generally. You're harder to move.</t>
@@ -1606,9 +1664,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Trust the Harness</t>
@@ -1619,14 +1677,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>While wearing Full Plate, when you would choose an armored Zone for a Graze, you may choose the Torso even if another rule would normally require another Zone.</t>
@@ -1637,9 +1695,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Lock Down ❶</t>
@@ -1650,14 +1708,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <r>
@@ -1666,11 +1724,20 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>:
 +1 Condition bonus to Physical Guard.
 You cannot be forcibly moved more than 3 feet by a single effect unless it critically succeeds.
@@ -1683,9 +1750,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Punishing Shove</t>
@@ -1696,13 +1763,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>When you push a foe away, you put the entire force of your Full Plate harness into it.</t>
@@ -1718,9 +1785,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Shoulder Check ❶</t>
@@ -1731,14 +1798,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <r>
@@ -1747,31 +1814,58 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Critical Success</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> The target is Wrong-Footed for you until the end of the next round.
 </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Success</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> The target is Wrong-Footed for you against the next Attack you attempt against it before the end of your next Opportunity.
 </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Critical Failure</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You are Wrong-Footed against melee attacks the target attempts against you until the end of the next round.</t>
           </r>
         </is>
@@ -1781,9 +1875,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Flowing Defense ❶</t>
@@ -1794,23 +1888,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Flowing Defense ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 While wearing Full Mail:
 when you Recenter, you may also Step;
@@ -1819,8 +1922,8 @@
           </r>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1833,21 +1936,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Your first Step each round ignores 1 point of Load Strain's effect on movement-related checks.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1860,21 +1963,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>When you are Grazed while wearing Full Mail, you may Step after resolving the attack and damage.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1887,14 +1990,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>When you would be Hit, shift the blow to another armored, non-Exposed Zone.</t>
@@ -1905,9 +2008,9 @@
           <t>Wits</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="I11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Layered Guard ❶</t>
@@ -1918,23 +2021,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Layered Guard ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 While wearing Full Scale:
 the first time each round a Zone becomes Exposed, another Zone of your choice gains +1 Protection until your next Opportunity.</t>
@@ -1946,9 +2058,9 @@
           <t>Wits</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Loose Guard</t>
@@ -1959,14 +2071,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>While all four Zones are Padded or Leather and your Load Strain is 0, Recenter lets you Step as part of the action.</t>
@@ -1977,9 +2089,9 @@
           <t>Agility</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="I13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Light on Your Feet ❶</t>
@@ -1990,23 +2102,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Armored Fighting Training</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Light on Your Feet ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 While in light armor:
 +1 Condition Physical Evade;
@@ -2020,7 +2141,7 @@
           <t>Agility</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2033,14 +2154,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -2093,8 +2212,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Brawling Training</t>
@@ -2110,9 +2234,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -2121,17 +2245,26 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Clinch ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> While you are in this stance, a bare hand counts as a rigid implement: you may Parry, Bind, and Gain Control with it, and a creature whose weapon or limb you Control with a bare hand is also Grabbed. At Master rank, a creature you have Grabbed cannot Recenter.</t>
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2144,21 +2277,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Brawling Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Your unarmed strikes deal 1d6 and count as weapons (lethal by default, your choice).</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2171,23 +2304,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Brawling Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Strike with a free hand; on a hit, the target is Off-Guard until your next Opportunity.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Crushing Grab</t>
@@ -2198,21 +2331,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Brawling Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>When you successfully Grapple a creature, you can deal bludgeoning damage to that creature equal to your Might bonus. You can make this attack nonlethal with no penalty.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2225,14 +2358,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -2285,8 +2416,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting Training</t>
@@ -2302,9 +2438,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -2313,11 +2449,20 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Brace the Stock ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 You settle into a firing position.
 Until you Move:
@@ -2328,17 +2473,26 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Move</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>.</t>
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2351,14 +2505,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Once per round, reduce the Reload value of a crossbow by 1, to a minimum of 1.</t>
@@ -2369,7 +2523,7 @@
           <t>Agility</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2382,21 +2536,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>When you spend an action Reloading, you may Step as part of that action.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2409,23 +2563,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Your Crossbow Strikes do an additional 2 damage against Exposed Zones.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Snap Shot</t>
@@ -2436,21 +2590,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>You may Intercept ❶↺ with a loaded crossbow that has the Close trait, if you have the Intercept Reaction.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2463,21 +2617,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Crossbow Fighting Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Take Cover, then Interact to reload. As normal, you must meet the requirements to Take Cover.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2490,14 +2644,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -2550,8 +2702,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Dueling Training</t>
@@ -2567,9 +2724,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -2578,26 +2735,49 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Hold the Cadence ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You must wield a single one-handed weapon with your other hand free. Name one creature as you enter the stance. That creature must answer your Strikes with the </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>same Defense it used against your previous Strike</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>, until you leave the stance or name another. At Master rank you may name a new creature ⓿.</t>
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2610,14 +2790,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Dueling Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>+1 Situation Guard vs. melee while wielding a one-handed weapon with your other hand free.</t>
@@ -2628,7 +2808,12 @@
           <t>Presence</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2641,23 +2826,28 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Dueling Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Feint, Strike, then Step.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Snagging Strike ❶</t>
@@ -2668,23 +2858,28 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Dueling Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>You combine an attack with quick grappling moves to throw an enemy off balance as long as it stays in your reach. Make a Strike while keeping one hand free. If this Strike hits, the target is Off-Guard until your next Opportunity or until it's no longer within the reach of your hand, whichever comes first.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Combat Grab ❶</t>
@@ -2695,31 +2890,22 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Dueling Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>Press</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>Requirements</t>
+            <t>Press
+Requirements</t>
           </r>
           <r>
             <t xml:space="preserve"> You have one hand free, and your target is within reach of that hand
@@ -2732,9 +2918,14 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Dueling Parry ❶</t>
@@ -2745,33 +2936,51 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Dueling Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Requirements</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You are wielding a single one-handed melee weapon and hold nothing else in your hands
 You can parry attacks against you with your one-handed weapon. You gain a +2 Situation bonus to </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <i val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Guard</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> until your next Opportunity as long as you continue to meet the requirements.</t>
           </r>
         </is>
@@ -2781,7 +2990,12 @@
           <t>Presence</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2794,14 +3008,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -2854,8 +3066,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Training</t>
@@ -2871,9 +3088,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -2882,21 +3099,35 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Overreach ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 You must be wielding a two-handed melee weapon.
 While you are in this stance your Hits and Critical Hits deal +2 damage and your Evade drops by 2, rising to +3 damage at Expert rank, +4 at Master, and +5 at Legendary. Every talent here requires this.</t>
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Sweeping Blow ❷</t>
@@ -2907,14 +3138,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <r>
@@ -2922,17 +3153,31 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Weighted</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>.</t>
           </r>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2945,14 +3190,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <r>
@@ -2960,19 +3205,33 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Weighted</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>.</t>
           </r>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Brutish Shove ❶</t>
@@ -2983,40 +3242,63 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Requirements</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You are wielding a two-handed melee weapon
 Using the momentum of your last attack to throw your weight into another, you make your opponent stumble back. Make a Strike with a two-handed melee weapon. If you hit a target that is your size or smaller, that creature is Off-Guard until your next Opportunity, and you can automatically Shove it, with the same benefits as the Shove action (including the Critical Success effect, if your Strike was a Critical Hit). If you move to follow the target, your movement doesn't trigger Reactions. This Strike has the following failure effect:
 </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Failure</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> The target becomes Off-Guard until your next Opportunity.</t>
           </r>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3029,21 +3311,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>When you make a Strike ❸ with a two-handed weapon, deal one extra weapon die of damage.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3056,21 +3343,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Great Weapon Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>If you Strike and it results in a Graze, you add your Might bonus to the damage.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3083,14 +3375,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -3143,8 +3433,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing Training</t>
@@ -3160,9 +3455,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -3173,17 +3468,8 @@
             <rPr>
               <b val="1"/>
             </rPr>
-            <t>Keep Moving ❶ Stance</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>Requirements</t>
+            <t>Keep Moving ❶ Stance
+Requirements</t>
           </r>
           <r>
             <t xml:space="preserve"> You wield a sling or a weapon with the Thrown trait.
@@ -3193,10 +3479,10 @@
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Quick Hand</t>
@@ -3207,23 +3493,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Draw a thrown weapon as part of the Strike made with it.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Running Cast</t>
@@ -3234,23 +3520,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>If you Moved at least 3 feet immediately before making a ranged Strike with a sling or thrown weapon, increase its Range by 10 feet for that Strike.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Harrying Shot</t>
@@ -3261,23 +3547,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>When you Graze with a sling or thrown weapon, the target takes a −1 Situation penalty to its next Attack before the end of the next round.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Trip Line</t>
@@ -3288,14 +3574,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <r>
@@ -3303,19 +3589,28 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Trip</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Trait.</t>
           </r>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Rebounding Toss ❷</t>
@@ -3326,23 +3621,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Missile Skirmishing Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Requirements</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You are wielding a thrown weapon
 You bounce your weapon off one foe to strike another. Make a ranged Strike with a thrown weapon. If this Strike hits, the weapon rebounds toward an enemy within 10 feet of the original target. Make an additional Strike against this second target. Both are Quick Strikes.</t>
           </r>
@@ -3353,7 +3657,7 @@
           <t>Wits</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3366,14 +3670,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -3426,8 +3728,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting Training</t>
@@ -3443,9 +3750,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <r>
@@ -3454,26 +3761,44 @@
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Shield Wall ❶ Stance</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You must be wielding a shield. While you are in this stance your shield counts as </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Raised at all times</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>, without spending an action for it, but you cannot Move; you may only Step. At Master rank you may Move up to half your Speed while the stance holds.</t>
           </r>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3486,14 +3811,14 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>When attacked, Raise your Shield.</t>
@@ -3504,7 +3829,7 @@
           <t>Agility</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3517,23 +3842,23 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Reduce an attack's damage to you by your shield's hardness.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="105" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Aggressive Block ⓿</t>
@@ -3544,23 +3869,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Shield Block</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Trigger</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You use Shield Block, and the opponent that triggered Shield Block is adjacent to you and is your Size or smaller
 You push back as you block, knocking your foe away or off balance. You use your shield to push the triggering creature, either automatically Shoving it 3 feet or causing it to become Off-Guard until your next Opportunity. The triggering creature chooses whether to be moved or become Off-Guard. If it chooses to be moved, you choose the direction. If the Shove would cause it to hit a solid object or enter another creature's space, it must become Off-Guard instead of being moved.</t>
           </r>
@@ -3571,9 +3905,9 @@
           <t>Might</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Devoted Guardian ❶</t>
@@ -3584,41 +3918,59 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Requirements</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Your last action was to Raise a Shield.
 You adopt a wide stance, ready to defend both yourself and your chosen ward. Select one adjacent creature. As long as your shield is raised and the creature remains adjacent to you, the creature gains a +1 Situation bonus to their </t>
           </r>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <i val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Guard</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t>, or a +2 Situation bonus if the shield you raised was a tower shield.</t>
           </r>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Defensive Advance ❷</t>
@@ -3629,32 +3981,41 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
+              <sz val="11"/>
             </rPr>
             <t>Flourish</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 With the protection of your shield, you dive into battle! You Raise your Shield and Move. If you end your movement within melee reach of at least one enemy, you can make a melee Strike against that enemy. You can use Defensive Advance while Burrowing, Climbing, Flying, or Swimming instead of Moving if you have the corresponding movement type.</t>
           </r>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Shield Warfare</t>
@@ -3665,21 +4026,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Shield Fighting Training</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>You know how to use shields offensively far better than most. Increase the weapon damage die of any shield bash, shield boss, or shield spikes you wield by one step.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/combat_styles.xlsx
+++ b/data/combat_styles.xlsx
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -833,6 +833,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -884,6 +886,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1138,6 +1145,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1189,6 +1198,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1355,6 +1369,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1406,6 +1422,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1562,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1592,6 +1615,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2192,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2215,6 +2245,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2368,6 +2403,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2419,6 +2456,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2654,6 +2696,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2705,6 +2749,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3018,6 +3067,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3069,6 +3120,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3441,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3438,6 +3496,11 @@
           <t>Enabled?</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3658,6 +3721,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3670,7 +3738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3680,6 +3748,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3733,6 +3803,11 @@
           <t>Enabled?</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
